--- a/tables and figures/methodology/03_Modeling_and_Evaluation.xlsx
+++ b/tables and figures/methodology/03_Modeling_and_Evaluation.xlsx
@@ -10,12 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contents" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="control_and_test_process" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="evaluation_metric_defs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="exploratory_metric_criteria" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="model_walkthrough_arch" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="models_and_tests" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pax_arrival_parameters" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lead_lag_timeline" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="probabilistic_metrics" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="model_walkthrough_arch" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="models_and_tests" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pax_arrival_parameters" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lead_lag_timeline" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="probabilistic_metrics" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -551,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -683,220 +682,188 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Table 3.3</t>
+          <t>Table 3.4</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>exploratory_metric_criteria</t>
+          <t>model_walkthrough_arch</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Exploratory Model Benchmarking Across Candidate Architectures and Regimes</t>
+          <t>Candidate Predictive Modeling Architectures and Evaluation Pipeline Stages</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Preliminary evaluation metrics across baseline and exploratory hybrid variants</t>
+          <t>Three-model candidate architecture specification, subcomponents, and holdout windows</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>9 rows x 6 cols</t>
+          <t>4 rows x 5 cols</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Preliminary Model Selection</t>
+          <t>Model Family Pipeline</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Table 3.4</t>
+          <t>Table 3.5</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>model_walkthrough_arch</t>
+          <t>models_and_tests</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Candidate Predictive Modeling Architectures and Evaluation Pipeline Stages</t>
+          <t>Empirical Comparison: Deterministic Flight Schedule Model Versus Dynamic Hybrid Model</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Three-model candidate architecture specification, subcomponents, and holdout windows</t>
+          <t>Empirical findings across arrival convolution, delay feedback, robustness, and transfer</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>4 rows x 5 cols</t>
+          <t>4 rows x 4 cols</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Model Family Pipeline</t>
+          <t>Architectural Synthesis</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Table 3.5</t>
+          <t>Table 3.6</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>models_and_tests</t>
+          <t>pax_arrival_parameters</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Empirical Comparison: Deterministic Flight Schedule Model Versus Dynamic Hybrid Model</t>
+          <t>Passenger Stochastic Arrival Kernel Parameters and Machine Learning Hyperparameters</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Empirical findings across arrival convolution, delay feedback, robustness, and transfer</t>
+          <t>Continuous Lognormal arrival density parameters, quantile losses, and GBDT settings</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>4 rows x 4 cols</t>
+          <t>3 rows x 5 cols</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Architectural Synthesis</t>
+          <t>Arrival Dynamics &amp; ML</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Table 3.6</t>
+          <t>Table 3.7</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>pax_arrival_parameters</t>
+          <t>lead_lag_timeline</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Passenger Stochastic Arrival Kernel Parameters and Machine Learning Hyperparameters</t>
+          <t>Physical Passenger Progression Timeline and Lead-Lag Horizon Specification</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Continuous Lognormal arrival density parameters, quantile losses, and GBDT settings</t>
+          <t>Temporal milestones from curbside arrival to screening, concourse dwell, and pushback</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>3 rows x 5 cols</t>
+          <t>5 rows x 4 cols</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Arrival Dynamics &amp; ML</t>
+          <t>Queuing &amp; Airport Geometry</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Table 3.7</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>lead_lag_timeline</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Physical Passenger Progression Timeline and Lead-Lag Horizon Specification</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Temporal milestones from curbside arrival to screening, concourse dwell, and pushback</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>5 rows x 4 cols</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Queuing &amp; Airport Geometry</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Table 3.8</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>probabilistic_metrics</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Probabilistic Forecast Verification Metrics and Model Selection Criteria</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>CRPS, PICP, AIC, and BIC definitions, mathematical formulations, and selection roles</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>4 rows x 5 cols</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Statistical Verification Metrics</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+    <row r="13" ht="22" customHeight="1"/>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Note. Master consolidated tabular dataset corresponding to figures in 03_Modeling_and_Evaluation. Formatted strictly according to APA Style (7th ed.) with horizontal boundary rules, zero auto-filters, and no background shading.</t>
         </is>
       </c>
     </row>
+    <row r="15" ht="24" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1188,15 +1155,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -1209,14 +1175,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Table 3.3</t>
+          <t>Table 3.4</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>Exploratory Model Benchmarking Across Candidate Architectures and Regimes</t>
+          <t>Candidate Predictive Modeling Architectures and Evaluation Pipeline Stages</t>
         </is>
       </c>
     </row>
@@ -1224,287 +1190,142 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Evaluation Dimension</t>
+          <t>Pipeline Operational Stage</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Performance Metric / Quality Criterion</t>
+          <t>Candidate Model Architecture</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Deterministic Benchmark (SARIMA)</t>
+          <t>Operational Modeling Paradigm</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Deep Recurrent Network (LSTM)</t>
+          <t>Algorithmic Subcomponent &amp; Loss Function</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Hybrid Variant 1 (Seasonal Switch)</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Two-Stage Dynamic Hybrid (Model 3)</t>
+          <t>Evaluation Window &amp; Testing Regimes</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>1. GENERALIZABILITY</t>
+          <t>Data Ingestion &amp; Feature Engineering</t>
         </is>
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>Mean MASE (efficiency)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="n">
-        <v>1.1843</v>
-      </c>
-      <c r="D6" s="21" t="n">
-        <v>3.2395</v>
-      </c>
-      <c r="E6" s="21" t="n">
-        <v>1.6888</v>
-      </c>
-      <c r="F6" s="21" t="n">
-        <v>1.3284</v>
+          <t>All Candidate Models</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>Preprocessing</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>TSA FOIA (3.07M rows) &amp; BTS OTP (12.7M flights) processed into Standardized Preprocessing &amp; Master Feature Pool</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>May 2022 to December 2024</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>1. GENERALIZABILITY</t>
+          <t>Candidate Model 1</t>
         </is>
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>SD of MASE (consistency)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="n">
-        <v>0.2528</v>
-      </c>
-      <c r="D7" s="21" t="n">
-        <v>2.6054</v>
-      </c>
-      <c r="E7" s="21" t="n">
-        <v>0.7081</v>
-      </c>
-      <c r="F7" s="21" t="n">
-        <v>0.3084</v>
+          <t>Deterministic Flight Schedule Model</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Deterministic Operational Baseline</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>Linear Schedule Seasonality with Stepwise Parameter Selection (AIC/BIC)</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Out-of-Sample Holdout (2025): Robustness, Resilience, Generalizability</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>1. GENERALIZABILITY</t>
+          <t>Candidate Model 2</t>
         </is>
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Hub Performance Gap (MAPE)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>0.44%</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>5.32%</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>0.51%</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>0.25%</t>
+          <t>Supervised Machine Learning Model</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>Automated Tree Regressor</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>Dynamic Parametric Variance D(mu, sigma) with Feature Embeddings and 24 OTP Features</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>Out-of-Sample Holdout (2025): Robustness, Resilience, Generalizability</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>2. RESILIENCE</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>Winter/Overall Error Ratio</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="n">
-        <v>1.5594</v>
-      </c>
-      <c r="D9" s="21" t="n">
-        <v>1.1223</v>
-      </c>
-      <c r="E9" s="21" t="n">
-        <v>1.9288</v>
-      </c>
-      <c r="F9" s="21" t="n">
-        <v>1.4688</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>2. RESILIENCE</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>Max Daily % Error (worst case)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>1165.75%</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>1428.13%</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>1387.96%</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>1142.15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>2. RESILIENCE</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>Winter Dominance Correlation</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="n">
-        <v>0.3291</v>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>0.1617</v>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>0.1617</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>0.3569</v>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>3. ROBUSTNESS</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>Weekday-Weekend Gap (MAPE)</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>6.05%</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>4.56%</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
-        <is>
-          <t>6.00%</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="inlineStr">
-        <is>
-          <t>5.40%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>3. ROBUSTNESS</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>Daily Error Volatility (SD)</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="n">
-        <v>38.5335</v>
-      </c>
-      <c r="D13" s="21" t="n">
-        <v>50.694</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>42.6858</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>41.0254</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>3. ROBUSTNESS</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>Data Reduction Degradation</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>-0.19%</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>-0.18%</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>-0.15%</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>-0.13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Note. Preliminary exploratory performance benchmarks across preliminary baseline and hybrid model formulations across Generalizability, Resilience, and Robustness dimensions.</t>
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>Candidate Model 3</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Dynamic Two-Stage Hybrid Model</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>Two-Stage Sequential Hybrid</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Stage 1: Linear Schedule Trend -&gt; Stage 2: Quantile Decision Tree on Residuals (SHAP / 1-Step Error Innovation Feedback e_{t-1})</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Out-of-Sample Holdout (2025): Robustness, Resilience, Generalizability</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Note. Architectural pipeline specification detailing preprocessing, algorithmic subcomponents, operational paradigms, and out-of-sample holdout windows for the three candidate models.</t>
         </is>
       </c>
     </row>
@@ -1525,11 +1346,10 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -1542,14 +1362,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Table 3.4</t>
+          <t>Table 3.5</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>Candidate Predictive Modeling Architectures and Evaluation Pipeline Stages</t>
+          <t>Empirical Comparison: Deterministic Flight Schedule Model Versus Dynamic Hybrid Model</t>
         </is>
       </c>
     </row>
@@ -1557,142 +1377,122 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Pipeline Operational Stage</t>
+          <t>Methodological Research Test</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Candidate Model Architecture</t>
+          <t>Model 1: Deterministic Schedule Baseline</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Operational Modeling Paradigm</t>
+          <t>Model 3: Dynamic Two-Stage Hybrid Model</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Algorithmic Subcomponent &amp; Loss Function</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Evaluation Window &amp; Testing Regimes</t>
+          <t>Empirical Finding &amp; Statistical Proof</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>Data Ingestion &amp; Feature Engineering</t>
+          <t>Arrival Timing</t>
         </is>
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>All Candidate Models</t>
+          <t>Assumes passenger flow is contemporaneous with flight departure (t).</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>Preprocessing</t>
+          <t>Convolves scheduled seats across a continuous probability density curve peaking at t + 2.</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>TSA FOIA (3.07M rows) &amp; BTS OTP (12.7M flights) processed into Standardized Preprocessing &amp; Master Feature Pool</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>May 2022 to December 2024</t>
+          <t>Convolving arrival probability raised explained variance from 19.88% to 48.78% (+145% gain).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>Candidate Model 1</t>
+          <t>Delay Feedback</t>
         </is>
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>Deterministic Flight Schedule Model</t>
+          <t>Static schedule only; blind to flight delays.</t>
         </is>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>Deterministic Operational Baseline</t>
+          <t>Ingests lagged operational congestion signals (DepDelay_{t-1}, Cancels_{t-1}).</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>Linear Schedule Seasonality with Stepwise Parameter Selection (AIC/BIC)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>Out-of-Sample Holdout (2025): Robustness, Resilience, Generalizability</t>
+          <t>Slashed holdout error by 91.3 pax/hr (29.1%) over status-quo scheduling (from 313.4 to 222.1 pax/hr).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>Candidate Model 2</t>
+          <t>Routine Stability (Robustness)</t>
         </is>
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Supervised Machine Learning Model</t>
+          <t>Fails against naive persistence (MASE = 0.945 vs Baseline Control MASE = 1.000).</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>Automated Tree Regressor</t>
+          <t>Significantly outperforms naive persistence (MASE_routine = 0.662</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>Dynamic Parametric Variance D(mu, sigma) with Feature Embeddings and 24 OTP Features</t>
+          <t>RMSE = 222.1 pax/hr).</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>Out-of-Sample Holdout (2025): Robustness, Resilience, Generalizability</t>
+          <t>The Diebold-Mariano test proved statistically significant superiority (DM = 48.72, p &lt; 0.0001).</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>Candidate Model 3</t>
+          <t>Spatial Transfer (Generalizability)</t>
         </is>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Dynamic Two-Stage Hybrid Model</t>
+          <t>Preserves stable transfer geometry (RMSE = 326.5 pax/hr; RTR = 1.04).</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>Two-Stage Sequential Hybrid</t>
+          <t>Overfits local terminal layout and innovation feedback (RMSE = 264.3 pax/hr; RTR = 1.19).</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>Stage 1: Linear Schedule Trend -&gt; Stage 2: Quantile Decision Tree on Residuals (SHAP / 1-Step Error Innovation Feedback e_{t-1})</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>Out-of-Sample Holdout (2025): Robustness, Resilience, Generalizability</t>
+          <t>Model 1 maintained lowest zero-shot transfer degradation (+4.2% RMSE increase and +4.0% DeltaMASE vs Model 3 +19.0% RMSE increase and +21.5% DeltaMASE).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>Note. Architectural pipeline specification detailing preprocessing, algorithmic subcomponents, operational paradigms, and out-of-sample holdout windows for the three candidate models.</t>
+          <t>Note. Empirical comparative findings across arrival timing convolution, delay feedback integration, routine operational accuracy (robustness), and spatial transferability (generalizability).</t>
         </is>
       </c>
     </row>
@@ -1705,173 +1505,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>⬅ Return to Table of Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>Table 3.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>Empirical Comparison: Deterministic Flight Schedule Model Versus Dynamic Hybrid Model</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Methodological Research Test</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Model 1: Deterministic Schedule Baseline</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Model 3: Dynamic Two-Stage Hybrid Model</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Empirical Finding &amp; Statistical Proof</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>Arrival Timing</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>Assumes passenger flow is contemporaneous with flight departure (t).</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>Convolves scheduled seats across a continuous probability density curve peaking at t + 2.</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>Convolving arrival probability raised explained variance from 19.88% to 48.78% (+145% gain).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>Delay Feedback</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>Static schedule only; blind to flight delays.</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>Ingests lagged operational congestion signals (DepDelay_{t-1}, Cancels_{t-1}).</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>Slashed holdout error by 91.3 pax/hr (29.1%) over status-quo scheduling (from 313.4 to 222.1 pax/hr).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>Routine Stability (Robustness)</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>Fails against naive persistence (MASE = 0.945 vs Baseline Control MASE = 1.000).</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>Significantly outperforms naive persistence (MASE_routine = 0.662</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>RMSE = 222.1 pax/hr).</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>The Diebold-Mariano test proved statistically significant superiority (DM = 48.72, p &lt; 0.0001).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>Spatial Transfer (Generalizability)</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>Preserves stable transfer geometry (RMSE = 326.5 pax/hr; RTR = 1.04).</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>Overfits local terminal layout and innovation feedback (RMSE = 264.3 pax/hr; RTR = 1.19).</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>Model 1 maintained lowest zero-shot transfer degradation (+4.2% RMSE increase and +4.0% DeltaMASE vs Model 3 +19.0% RMSE increase and +21.5% DeltaMASE).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Note. Empirical comparative findings across arrival timing convolution, delay feedback integration, routine operational accuracy (robustness), and spatial transferability (generalizability).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2032,7 +1665,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2216,7 +1849,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/tables and figures/methodology/03_Modeling_and_Evaluation.xlsx
+++ b/tables and figures/methodology/03_Modeling_and_Evaluation.xlsx
@@ -23,9 +23,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="9">
     <font>
       <name val="Calibri"/>
@@ -116,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -169,15 +167,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -551,10 +540,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -682,7 +671,7 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Table 3.4</t>
+          <t>Table 3.3</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -714,7 +703,7 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Table 3.5</t>
+          <t>Table 3.4</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -746,7 +735,7 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Table 3.6</t>
+          <t>Table 3.5</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -778,7 +767,7 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Table 3.7</t>
+          <t>Table 3.6</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -810,7 +799,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Table 3.8</t>
+          <t>Table 3.7</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
@@ -839,31 +828,29 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1"/>
-    <row r="14">
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Note. Master consolidated tabular dataset corresponding to figures in 03_Modeling_and_Evaluation. Formatted strictly according to APA Style (7th ed.) with horizontal boundary rules, zero auto-filters, and no background shading.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -876,7 +863,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="43" customWidth="1" min="2" max="2"/>
@@ -1016,7 +1003,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
@@ -1156,7 +1143,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
@@ -1175,7 +1162,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Table 3.4</t>
+          <t>Table 3.3</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1331,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
@@ -1362,7 +1349,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Table 3.5</t>
+          <t>Table 3.4</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1498,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
@@ -1530,7 +1517,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Table 3.6</t>
+          <t>Table 3.5</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1659,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
@@ -1690,7 +1677,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Table 3.7</t>
+          <t>Table 3.6</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1843,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
@@ -1875,7 +1862,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Table 3.8</t>
+          <t>Table 3.7</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1912,7 @@
           <t>Continuous Ranked Probability Score</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>CRPS</t>
         </is>
@@ -1952,7 +1939,7 @@
           <t>Prediction Interval Coverage Probability</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>PICP</t>
         </is>
@@ -1979,7 +1966,7 @@
           <t>Akaike Information Criterion</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>AIC</t>
         </is>
@@ -2006,7 +1993,7 @@
           <t>Bayesian Information Criterion</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>BIC</t>
         </is>

--- a/tables and figures/methodology/03_Modeling_and_Evaluation.xlsx
+++ b/tables and figures/methodology/03_Modeling_and_Evaluation.xlsx
@@ -57,9 +57,8 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="000563C1"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <u val="single"/>
     </font>
     <font>
